--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17BA334-D9F0-4E6A-BAD4-A8326E64B1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD006FD-181D-46D3-8172-E39F31E97AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="synthèse" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -310,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -345,6 +346,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,21 +627,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.69140625" customWidth="1"/>
-    <col min="2" max="2" width="14.07421875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="17" style="10" customWidth="1"/>
     <col min="3" max="3" width="47.84375" customWidth="1"/>
     <col min="4" max="4" width="9" style="10" customWidth="1"/>
     <col min="5" max="5" width="13.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="37.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="37.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="13" t="s">
         <v>52</v>
       </c>
       <c r="C1" s="6" t="s">
@@ -652,7 +654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1060,12 +1062,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A26" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>16</v>
@@ -1073,16 +1075,16 @@
       <c r="D26" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>36</v>
@@ -1090,16 +1092,16 @@
       <c r="D27" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E27" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A28" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>27</v>
@@ -1107,16 +1109,16 @@
       <c r="D28" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E28" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>28</v>
@@ -1124,16 +1126,16 @@
       <c r="D29" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E29" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A30" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>33</v>
@@ -1141,11 +1143,11 @@
       <c r="D30" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1153,16 +1155,16 @@
         <v>57</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E31" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E31">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" s="7" t="s">
         <v>5</v>
       </c>
@@ -1170,16 +1172,16 @@
         <v>57</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E32" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E32" s="8">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" s="7" t="s">
         <v>5</v>
       </c>
@@ -1187,16 +1189,16 @@
         <v>57</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E33" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E33" s="8">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" s="7" t="s">
         <v>5</v>
       </c>
@@ -1204,16 +1206,16 @@
         <v>57</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E34" s="8">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" s="7" t="s">
         <v>5</v>
       </c>
@@ -1221,13 +1223,13 @@
         <v>57</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E35" s="10">
-        <v>1</v>
+      <c r="E35" s="8">
+        <v>29.8</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
@@ -1238,12 +1240,12 @@
         <v>57</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="8">
         <v>29.8</v>
       </c>
     </row>
@@ -1255,7 +1257,7 @@
         <v>57</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>63</v>
@@ -1272,7 +1274,7 @@
         <v>57</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>63</v>
@@ -1289,7 +1291,7 @@
         <v>57</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>63</v>
@@ -1306,7 +1308,7 @@
         <v>57</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>63</v>
@@ -1323,7 +1325,7 @@
         <v>57</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>63</v>
@@ -1340,13 +1342,13 @@
         <v>57</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E42" s="8">
-        <v>29.8</v>
+      <c r="E42">
+        <v>273</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
@@ -1357,13 +1359,13 @@
         <v>57</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E43" s="8">
-        <v>29.8</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
@@ -1374,13 +1376,13 @@
         <v>57</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="8">
-        <v>29.8</v>
+      <c r="E44">
+        <v>25200</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
@@ -1391,13 +1393,13 @@
         <v>57</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="8">
-        <v>29.8</v>
+      <c r="E45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
@@ -1408,115 +1410,121 @@
         <v>57</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E46" s="8">
-        <v>29.8</v>
+      <c r="E46">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A47" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>57</v>
+      <c r="A47" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E47">
-        <v>273</v>
+      <c r="E47" s="10">
+        <f>1*0.27</f>
+        <v>0.27</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A48" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>57</v>
+      <c r="A48" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E48" s="8">
-        <v>273</v>
+      <c r="E48" s="10">
+        <f t="shared" ref="E48:E56" si="0">1*0.27</f>
+        <v>0.27</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A49" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>57</v>
+      <c r="A49" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E49">
-        <v>25200</v>
+      <c r="E49" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A50" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>57</v>
+      <c r="A50" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E50">
-        <v>1</v>
+      <c r="E50" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A51" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>57</v>
+      <c r="A51" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E51">
-        <v>1</v>
+      <c r="E51" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
+        <v>67</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
@@ -1527,13 +1535,13 @@
         <v>67</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E53" s="10">
-        <f>1*0.27</f>
+        <f t="shared" si="0"/>
         <v>0.27</v>
       </c>
     </row>
@@ -1545,13 +1553,13 @@
         <v>67</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E54" s="10">
-        <f t="shared" ref="E54:E62" si="0">1*0.27</f>
+        <f t="shared" si="0"/>
         <v>0.27</v>
       </c>
     </row>
@@ -1563,7 +1571,7 @@
         <v>67</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>63</v>
@@ -1581,7 +1589,7 @@
         <v>67</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>63</v>
@@ -1599,14 +1607,14 @@
         <v>67</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E57" s="10">
-        <f t="shared" si="0"/>
-        <v>0.27</v>
+        <f>29.8*0.27</f>
+        <v>8.0460000000000012</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
@@ -1617,14 +1625,14 @@
         <v>67</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E58" s="10">
-        <f t="shared" si="0"/>
-        <v>0.27</v>
+        <f t="shared" ref="E58:E67" si="1">29.8*0.27</f>
+        <v>8.0460000000000012</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
@@ -1635,14 +1643,14 @@
         <v>67</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E59" s="10">
-        <f t="shared" si="0"/>
-        <v>0.27</v>
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
@@ -1653,14 +1661,14 @@
         <v>67</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E60" s="10">
-        <f t="shared" si="0"/>
-        <v>0.27</v>
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
@@ -1671,14 +1679,14 @@
         <v>67</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E61" s="10">
-        <f t="shared" si="0"/>
-        <v>0.27</v>
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
@@ -1689,14 +1697,14 @@
         <v>67</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E62" s="10">
-        <f t="shared" si="0"/>
-        <v>0.27</v>
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
@@ -1707,13 +1715,13 @@
         <v>67</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E63" s="10">
-        <f>29.8*0.27</f>
+        <f t="shared" si="1"/>
         <v>8.0460000000000012</v>
       </c>
     </row>
@@ -1725,17 +1733,17 @@
         <v>67</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E64" s="10">
-        <f t="shared" ref="E64:E73" si="1">29.8*0.27</f>
+        <f t="shared" si="1"/>
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65" s="11" t="s">
         <v>5</v>
       </c>
@@ -1743,7 +1751,7 @@
         <v>67</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>63</v>
@@ -1753,7 +1761,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66" s="11" t="s">
         <v>5</v>
       </c>
@@ -1761,7 +1769,7 @@
         <v>67</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>63</v>
@@ -1771,7 +1779,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67" s="11" t="s">
         <v>5</v>
       </c>
@@ -1779,7 +1787,7 @@
         <v>67</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>63</v>
@@ -1789,7 +1797,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" s="11" t="s">
         <v>5</v>
       </c>
@@ -1797,197 +1805,198 @@
         <v>67</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>63</v>
       </c>
       <c r="E68" s="10">
-        <f t="shared" si="1"/>
-        <v>8.0460000000000012</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A69" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E69" s="10">
-        <f t="shared" si="1"/>
-        <v>8.0460000000000012</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A70" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E70" s="10">
-        <f t="shared" si="1"/>
-        <v>8.0460000000000012</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A71" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E71" s="10">
-        <f t="shared" si="1"/>
-        <v>8.0460000000000012</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A72" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E72" s="10">
-        <f t="shared" si="1"/>
-        <v>8.0460000000000012</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A73" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E73" s="10">
-        <f t="shared" si="1"/>
-        <v>8.0460000000000012</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A74" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E74" s="10">
         <f>273*0.27</f>
         <v>73.710000000000008</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A75" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C75" s="4" t="s">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A69" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E75" s="10">
+      <c r="D69" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E69" s="10">
         <f>273*0.27</f>
         <v>73.710000000000008</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A76" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C76" s="4" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A70" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E76" s="10">
+      <c r="D70" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E70" s="10">
         <f>25200*0.27</f>
         <v>6804</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A77" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C77" s="4" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A71" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E77" s="10">
+      <c r="D71" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E71" s="10">
         <f>1*0.27</f>
         <v>0.27</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A78" s="11" t="s">
-        <v>5</v>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A72" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E72" s="10">
+        <f t="shared" ref="E72" si="2">1*0.27</f>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A73" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E73" s="10">
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
+      </c>
+      <c r="F73" s="14"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A74" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E74" s="10">
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A75" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E75" s="10">
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A76" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E76" s="10">
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A77" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E77" s="10">
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A78" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>67</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E78" s="10">
-        <f t="shared" ref="E78:E79" si="2">1*0.27</f>
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" s="7" t="s">
         <v>4</v>
       </c>
@@ -1995,17 +2004,17 @@
         <v>67</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E79" s="10">
-        <f t="shared" si="2"/>
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80" s="7" t="s">
         <v>4</v>
       </c>
@@ -2013,14 +2022,14 @@
         <v>67</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E80" s="10">
-        <f>1*0.9</f>
-        <v>0.9</v>
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.4">
@@ -2031,14 +2040,14 @@
         <v>67</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E81" s="10">
-        <f t="shared" ref="E81:E91" si="3">1*0.9</f>
-        <v>0.9</v>
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.4">
@@ -2049,14 +2058,14 @@
         <v>67</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E82" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.4">
@@ -2067,14 +2076,14 @@
         <v>67</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E83" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.4">
@@ -2085,14 +2094,14 @@
         <v>67</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E84" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.4">
@@ -2103,14 +2112,14 @@
         <v>67</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E85" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
+        <f>(1*0.9)*1000000</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.4">
@@ -2121,122 +2130,31 @@
         <v>67</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E86" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
+        <f>(1*0.95)*1000000</f>
+        <v>950000</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A87" s="7" t="s">
-        <v>4</v>
+      <c r="A87" s="11" t="s">
+        <v>6</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E87" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A88" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E88" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A89" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E89" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A90" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E90" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A91" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E91" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A92" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E92" s="10">
-        <f>1*0.95</f>
-        <v>0.95</v>
+        <v>59</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2244,4 +2162,99 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF990EF-DE90-47BF-B8CD-C4AE8A165117}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD006FD-181D-46D3-8172-E39F31E97AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1C7590-F658-46A8-A4D3-E45738E6BAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1C7590-F658-46A8-A4D3-E45738E6BAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FBF035-8AC9-4AAC-9F24-C852232A0071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="synthèse" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
+    <sheet name="synthèse" sheetId="5" r:id="rId1"/>
+    <sheet name="synthèse v3" sheetId="4" r:id="rId2"/>
+    <sheet name="synthèse v2" sheetId="1" r:id="rId3"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId4"/>
+    <sheet name="Feuil2" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="219">
   <si>
     <t>NH3 - agriculture - air</t>
   </si>
@@ -242,13 +245,466 @@
   </si>
   <si>
     <t>Biodiv</t>
+  </si>
+  <si>
+    <t>Forest area - Forestry</t>
+  </si>
+  <si>
+    <t>Permanent pastures - Grazing-Cattle</t>
+  </si>
+  <si>
+    <t>Permanent pastures - Grazing-Meat animals nec</t>
+  </si>
+  <si>
+    <t>Permanent pastures - Grazing-Raw milk</t>
+  </si>
+  <si>
+    <t>Forest area - Marginal use</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - rice</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - wheat</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - other cereals</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - roots and tubers</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - sugar crops</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - pulses</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - nuts</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - oil crops</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - vegetables</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - fruits</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - fibres</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - other crops</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Agriculture - fodder crops</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - dairy cattle</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - nondairy cattle</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - pigs</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - sheep</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - goats</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - buffaloes</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - camels</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - horses</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - chicken</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - turkeys</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - ducks</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Livestock - geese</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Products of meat cattle</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Products of meat pigs</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Products of meat poultry</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Meat products nec</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - products of Vegetable oils and fats</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Dairy products</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Processed rice</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Sugar</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Food products nec</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Beverages</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Fish products</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Tobacco products (16)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Textiles (17)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Wearing apparel; furs (18)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Leather and leather products (19)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Pulp</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Secondary paper for treatment, Re-processing of secondary paper into new pulp</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Paper and paper products</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Printed matter and recorded media (22)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Plastics, basic</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Secondary plastic for treatment, Re-processing of secondary plastic into new plastic</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - N-fertiliser</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - P- and other fertiliser</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Chemicals nec</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Rubber and plastic products (25)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Glass and glass products</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Secondary glass for treatment, Re-processing of secondary glass into new glass</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Ceramic goods</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Bricks, tiles and construction products, in baked clay</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Cement, lime and plaster</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Ash for treatment, Re-processing of ash into clinker</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Other non-metallic mineral products</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Basic iron and steel and of ferro-alloys and first products thereof</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Secondary steel for treatment, Re-processing of secondary steel into new steel</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Precious metals</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Secondary preciuos metals for treatment, Re-processing of secondary preciuos metals into new preciuos metals</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Aluminium and aluminium products</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Secondary aluminium for treatment, Re-processing of secondary aluminium into new aluminium</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Lead, zinc and tin and products thereof</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Secondary lead for treatment, Re-processing of secondary lead into new lead</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Copper products</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Secondary copper for treatment, Re-processing of secondary copper into new copper</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Other non-ferrous metal products</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Secondary other non-ferrous metals for treatment, Re-processing of secondary other non-ferrous metals into new other non-ferrous metals</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Fabricated metal products, except machinery and equipment (28)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Machinery and equipment n.e.c. (29)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Office machinery and computers (30)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Electrical machinery and apparatus n.e.c. (31)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Radio, television and communication equipment and apparatus (32)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Medical, precision and optical instruments, watches and clocks (33)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Motor vehicles, trailers and semi-trailers (34)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Other transport equipment (35)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Manufacturing - Furniture; other manufactured goods n.e.c. (36)</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by coal</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by gas</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by nuclear</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by hydro</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by wind</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by petroleum and other oil derivatives</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by biomass and waste</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by solar photovoltaic</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by solar thermal</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by tide, wave, ocean</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity by Geothermal</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - tower - Electricity nec</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by coal</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by gas</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by nuclear</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by hydro</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by wind</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by petroleum and other oil derivatives</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by biomass and waste</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by solar photovoltaic</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by solar thermal</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by tide, wave, ocean</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity by Geothermal</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Electricity - once-through - Electricity nec</t>
+  </si>
+  <si>
+    <t>Water Consumption Blue - Domestic - domestic Water Consumption Blue</t>
+  </si>
+  <si>
+    <t>Artificial Surfaces</t>
+  </si>
+  <si>
+    <t>Cropland - cropped area - Cereal grains nec</t>
+  </si>
+  <si>
+    <t>Cropland - cropped area - Crops nec</t>
+  </si>
+  <si>
+    <t>Cropland - cropped area - Oil seeds</t>
+  </si>
+  <si>
+    <t>Cropland - cropped area - Paddy rice</t>
+  </si>
+  <si>
+    <t>Cropland - cropped area - Plant-based fibers</t>
+  </si>
+  <si>
+    <t>Cropland - cropped area - Sugar cane, sugar beet</t>
+  </si>
+  <si>
+    <t>Cropland - cropped area - Vegetables, fruit, nuts</t>
+  </si>
+  <si>
+    <t>Cropland - cropped area - Wheat</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area - Cereal grains nec</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area - Crops nec</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area - Oil seeds</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area - Paddy rice</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area - Plant-based fibers</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area - Sugar cane, sugar beet</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area - Vegetables, fruit, nuts</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area - Wheat</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area-Cattle</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area-Meat animals nec</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area-Pigs</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area-Poultry</t>
+  </si>
+  <si>
+    <t>Cropland - fallowed area-Raw milk</t>
+  </si>
+  <si>
+    <t>Forest</t>
+  </si>
+  <si>
+    <t>Energy use - Final</t>
+  </si>
+  <si>
+    <t>CO2 - waste - biogenic - air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2 </t>
+  </si>
+  <si>
+    <t>ghg_combustion</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
+    <t>N2O</t>
+  </si>
+  <si>
+    <t>SF6</t>
+  </si>
+  <si>
+    <t>HFC</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>raw_materials</t>
+  </si>
+  <si>
+    <t>RMC</t>
+  </si>
+  <si>
+    <t>MtCO2eq</t>
+  </si>
+  <si>
+    <t>kt</t>
+  </si>
+  <si>
+    <t>GHG emissions</t>
+  </si>
+  <si>
+    <t>Cropland use</t>
+  </si>
+  <si>
+    <t>P surplus</t>
+  </si>
+  <si>
+    <t>N surplus</t>
+  </si>
+  <si>
+    <t>Biodiversity loss</t>
+  </si>
+  <si>
+    <t>Raw material consumption</t>
+  </si>
+  <si>
+    <t>Blue water consumption</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +730,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -311,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -347,6 +808,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,8 +1093,6554 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D0163B-5317-4028-ABDC-4C843EF1CC69}">
+  <dimension ref="A1:F171"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.69140625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="17" style="10" customWidth="1"/>
+    <col min="3" max="3" width="47.84375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9" style="10" customWidth="1"/>
+    <col min="5" max="5" width="13.23046875" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9.23046875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="14">
+        <v>1.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="14">
+        <v>8.2400000000000005E-10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="14">
+        <v>3E-10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="14">
+        <v>3E-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A41" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A42" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A43" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A45" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A46" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A47" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A48" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A49" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A50" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A51" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A52" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A53" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A54" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A55" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A56" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A57" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A58" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A59" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A60" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E60" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A61" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A62" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E62" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E63" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E64" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A65" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E65" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A66" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A67" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E67" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A68" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E68" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A69" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A70" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E70" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A71" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E71" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A72" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E72" s="10">
+        <v>1</v>
+      </c>
+      <c r="F72" s="14"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A73" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E73" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A74" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E74" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A75" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E75" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A76" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E76" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A77" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E77" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A78" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E78" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A79" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A80" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E80" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E81" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A82" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E82" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A83" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E83" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A84" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E84" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A85" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E85" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A86" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E86" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A87" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E87" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A88" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E88" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A89" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E89" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A90" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E90" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A91" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E91" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A92" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E92" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A93" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E93" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A94" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E94" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A95" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E95" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A96" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E96" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A97" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E97" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A98" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E98" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A99" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E99" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A100" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E100" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A101" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E101" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A102" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E102" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A103" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E103" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A104" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E104" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A105" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E105" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A106" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E106" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A107" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E107" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A108" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E108" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A109" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E109" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A110" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E110" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A111" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E111" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A112" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E112" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A113" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E113" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A114" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E114" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A115" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E115" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A116" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E116" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A117" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E117" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A118" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E118" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A119" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E119" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A120" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E120" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A121" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E121" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A122" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E122" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A123" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E123" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A124" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E124" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A125" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E125" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A126" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E126" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A127" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E127" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A128" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E128" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A129" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E129" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A130" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E130" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A131" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E131" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A132" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E132" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A133" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E133" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A134" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E134" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A135" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E135" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A136" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E136" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A137" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E137" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A138" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E138" s="14">
+        <v>271000000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A139" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E139" s="14">
+        <v>271000000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A140" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E140" s="14">
+        <v>271000000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A141" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C141" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E141" s="14">
+        <v>271000000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A142" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C142" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E142" s="14">
+        <v>271000000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A143" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C143" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E143" s="14">
+        <v>271000000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A144" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C144" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E144" s="14">
+        <v>271000000</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A145" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E145" s="10">
+        <f>(1*0.95)*1000000</f>
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A146" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E146" s="10">
+        <f t="shared" ref="E146:E166" si="0">(1*0.88)*1000000</f>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A147" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E147" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A148" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E148" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A149" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E149" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A150" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E150" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A151" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E151" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A152" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E152" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A153" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E153" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A154" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E154" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A155" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E155" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A156" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E156" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A157" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E157" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A158" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E158" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A159" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E159" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A160" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E160" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A161" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E161" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A162" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E162" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A163" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E163" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A164" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E164" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A165" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E165" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A166" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E166" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A167" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B167" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E167" s="10">
+        <f>(1*0.17)*1000000</f>
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A168" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E168" s="10">
+        <f t="shared" ref="E168:E170" si="1">(1*0.4)*1000000</f>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A169" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E169" s="10">
+        <f>(1*0.4)*1000000</f>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A170" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E170" s="10">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A171" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B171" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E171" s="10">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDE2010-B659-4D8C-A3CE-548591F6AB6A}">
+  <dimension ref="A1:F207"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.69140625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="17" style="10" customWidth="1"/>
+    <col min="3" max="3" width="47.84375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9" style="10" customWidth="1"/>
+    <col min="5" max="5" width="13.23046875" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9.23046875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A41" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A42" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A43" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A45" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A46" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A47" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A48" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A49" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A50" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A51" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A52" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A53" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A54" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A55" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A56" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A57" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A58" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A59" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A60" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E60" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A61" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A62" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E62" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E63" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E64" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A65" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E65" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A66" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A67" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E67" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A68" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E68" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A69" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A70" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E70" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A71" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E71" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A72" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E72" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A73" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E73" s="10">
+        <v>1</v>
+      </c>
+      <c r="F73" s="14"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A74" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E74" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A75" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E75" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A76" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E76" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A77" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E77" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A78" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E78" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A79" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A80" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E80" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E81" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A82" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E82" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A83" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E83" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A84" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E84" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A85" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E85" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A86" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E86" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A87" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E87" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A88" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E88" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A89" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E89" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A90" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E90" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A91" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E91" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A92" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E92" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A93" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E93" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A94" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E94" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A95" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E95" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A96" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E96" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A97" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E97" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A98" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E98" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A99" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E99" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A100" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E100" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A101" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E101" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A102" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E102" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A103" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E103" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A104" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E104" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A105" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E105" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A106" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E106" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A107" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E107" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A108" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E108" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A109" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E109" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A110" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E110" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A111" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E111" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A112" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E112" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A113" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E113" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A114" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E114" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A115" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E115" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A116" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E116" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A117" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E117" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A118" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E118" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A119" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E119" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A120" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E120" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A121" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E121" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A122" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E122" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A123" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E123" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A124" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E124" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A125" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E125" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A126" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E126" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A127" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E127" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A128" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E128" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A129" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E129" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A130" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E130" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A131" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E131" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A132" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E132" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A133" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E133" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A134" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E134" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A135" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E135" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A136" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E136" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A137" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E137" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A138" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E138" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A139" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E139" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A140" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E140" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A141" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E141" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A142" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E142" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A143" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E143" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A144" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E144" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A145" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E145" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A146" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E146" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A147" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E147" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A148" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E148" s="10">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A149" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E149" s="10">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A150" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E150" s="10">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A151" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E151" s="10">
+        <v>25200</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A152" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E152" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A153" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E153" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A154" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E154" s="10">
+        <f>1*0.27</f>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A155" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E155" s="10">
+        <f t="shared" ref="E155:E164" si="0">1*0.27</f>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A156" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E156" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A157" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E157" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A158" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E158" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A159" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E159" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A160" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E160" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A161" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E161" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A162" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E162" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A163" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E163" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A164" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E164" s="10">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A165" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E165" s="10">
+        <f>29.8*0.27</f>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A166" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E166" s="10">
+        <f t="shared" ref="E166:E175" si="1">29.8*0.27</f>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A167" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B167" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E167" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A168" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E168" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A169" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E169" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A170" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E170" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A171" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B171" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E171" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A172" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E172" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A173" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B173" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E173" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A174" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B174" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E174" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A175" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B175" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E175" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0460000000000012</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A176" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E176" s="10">
+        <f>273*0.27</f>
+        <v>73.710000000000008</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A177" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B177" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E177" s="10">
+        <f>273*0.27</f>
+        <v>73.710000000000008</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A178" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B178" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E178" s="10">
+        <f>25200*0.27</f>
+        <v>6804</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A179" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B179" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E179" s="10">
+        <f>1*0.27</f>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A180" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B180" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E180" s="10">
+        <f t="shared" ref="E180" si="2">1*0.27</f>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A181" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B181" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E181" s="10">
+        <f>(1*0.95)*1000000</f>
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A182" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B182" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E182" s="10">
+        <f t="shared" ref="E182:E202" si="3">(1*0.88)*1000000</f>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A183" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B183" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E183" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A184" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B184" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C184" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E184" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A185" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B185" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C185" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E185" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A186" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B186" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E186" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A187" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B187" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E187" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A188" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B188" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E188" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A189" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B189" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C189" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E189" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A190" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B190" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E190" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A191" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B191" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C191" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E191" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A192" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B192" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E192" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A193" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B193" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E193" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A194" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B194" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E194" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A195" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B195" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E195" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A196" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B196" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E196" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A197" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B197" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C197" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E197" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A198" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B198" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E198" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A199" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B199" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E199" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A200" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B200" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E200" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A201" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B201" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E201" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A202" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B202" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E202" s="10">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A203" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B203" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C203" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E203" s="10">
+        <f>(1*0.17)*1000000</f>
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A204" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B204" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C204" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E204" s="10">
+        <f t="shared" ref="E204:E206" si="4">(1*0.4)*1000000</f>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A205" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B205" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C205" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E205" s="10">
+        <f>(1*0.4)*1000000</f>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A206" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B206" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C206" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E206" s="10">
+        <f t="shared" si="4"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A207" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B207" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E207" s="10">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.69140625" customWidth="1"/>
@@ -637,7 +7650,7 @@
     <col min="5" max="5" width="13.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="37.85" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -654,7 +7667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1901,8 +8914,8 @@
         <v>65</v>
       </c>
       <c r="E73" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f>(1*0.88)*1000000</f>
+        <v>880000</v>
       </c>
       <c r="F73" s="14"/>
     </row>
@@ -1920,8 +8933,8 @@
         <v>65</v>
       </c>
       <c r="E74" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" ref="E74:E85" si="3">(1*0.88)*1000000</f>
+        <v>880000</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.4">
@@ -1938,8 +8951,8 @@
         <v>65</v>
       </c>
       <c r="E75" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.4">
@@ -1956,8 +8969,8 @@
         <v>65</v>
       </c>
       <c r="E76" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.4">
@@ -1974,8 +8987,8 @@
         <v>65</v>
       </c>
       <c r="E77" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.4">
@@ -1992,8 +9005,8 @@
         <v>65</v>
       </c>
       <c r="E78" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.4">
@@ -2010,8 +9023,8 @@
         <v>65</v>
       </c>
       <c r="E79" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.4">
@@ -2028,8 +9041,8 @@
         <v>65</v>
       </c>
       <c r="E80" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.4">
@@ -2046,8 +9059,8 @@
         <v>65</v>
       </c>
       <c r="E81" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.4">
@@ -2064,8 +9077,8 @@
         <v>65</v>
       </c>
       <c r="E82" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.4">
@@ -2082,8 +9095,8 @@
         <v>65</v>
       </c>
       <c r="E83" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.4">
@@ -2100,8 +9113,8 @@
         <v>65</v>
       </c>
       <c r="E84" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
+        <f t="shared" si="3"/>
+        <v>880000</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.4">
@@ -2118,11 +9131,11 @@
         <v>65</v>
       </c>
       <c r="E85" s="10">
-        <f>(1*0.9)*1000000</f>
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A86" s="7" t="s">
         <v>4</v>
       </c>
@@ -2130,30 +9143,120 @@
         <v>67</v>
       </c>
       <c r="C86" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E86" s="10">
+        <f>(1*0.17)*1000000</f>
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E87" s="10">
+        <f>(1*0.17)*1000000</f>
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A88" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E88" s="10">
+        <f>(1*0.4)*1000000</f>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A89" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E89" s="10">
+        <f t="shared" ref="E89:E90" si="4">(1*0.4)*1000000</f>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A90" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E90" s="10">
+        <f t="shared" si="4"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A91" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C91" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E86" s="10">
+      <c r="D91" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E91" s="10">
         <f>(1*0.95)*1000000</f>
         <v>950000</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A87" s="11" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A92" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B92" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E87">
+      <c r="E92">
         <v>1</v>
       </c>
     </row>
@@ -2164,7 +9267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF990EF-DE90-47BF-B8CD-C4AE8A165117}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -2257,4 +9360,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C5D093-8CF0-451E-9E06-02EB1F70D6E7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FBF035-8AC9-4AAC-9F24-C852232A0071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CDE311-0258-4555-BAA6-F1A503B05757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="220">
   <si>
     <t>NH3 - agriculture - air</t>
   </si>
@@ -698,13 +698,16 @@
   </si>
   <si>
     <t>Blue water consumption</t>
+  </si>
+  <si>
+    <t>NOX - agriculture - air</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,6 +738,19 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -769,10 +785,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -814,9 +832,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{BF4AD094-E667-4039-A661-3E4B589FACBD}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{B82B8786-F10B-4C85-A6B3-FD5566113E64}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1094,12 +1120,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D0163B-5317-4028-ABDC-4C843EF1CC69}">
-  <dimension ref="A1:F171"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.69140625" style="10" customWidth="1"/>
     <col min="2" max="2" width="17" style="10" customWidth="1"/>
-    <col min="3" max="3" width="47.84375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="47.84375" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="10" customWidth="1"/>
     <col min="5" max="5" width="13.23046875" style="10" customWidth="1"/>
     <col min="6" max="16384" width="9.23046875" style="10"/>
@@ -1129,7 +1155,7 @@
       <c r="B2" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
@@ -1146,7 +1172,7 @@
       <c r="B3" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="18" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="12" t="s">
@@ -1161,16 +1187,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>215</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>63</v>
       </c>
       <c r="E4" s="14">
-        <v>3E-10</v>
+        <v>6.3599999999999998E-10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
@@ -1178,50 +1204,50 @@
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="14">
+        <v>3.0399999999999998E-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="14">
+        <v>3E-10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="D7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="14">
         <v>3E-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="10">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -1231,8 +1257,8 @@
       <c r="B8" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>75</v>
+      <c r="C8" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>64</v>
@@ -1248,8 +1274,8 @@
       <c r="B9" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>76</v>
+      <c r="C9" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>64</v>
@@ -1265,8 +1291,8 @@
       <c r="B10" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>77</v>
+      <c r="C10" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>64</v>
@@ -1282,8 +1308,8 @@
       <c r="B11" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>78</v>
+      <c r="C11" s="12" t="s">
+        <v>76</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>64</v>
@@ -1299,8 +1325,8 @@
       <c r="B12" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C12" s="16" t="s">
-        <v>79</v>
+      <c r="C12" s="12" t="s">
+        <v>77</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>64</v>
@@ -1316,8 +1342,8 @@
       <c r="B13" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>80</v>
+      <c r="C13" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>64</v>
@@ -1333,8 +1359,8 @@
       <c r="B14" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="16" t="s">
-        <v>81</v>
+      <c r="C14" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>64</v>
@@ -1350,8 +1376,8 @@
       <c r="B15" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C15" s="16" t="s">
-        <v>82</v>
+      <c r="C15" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>64</v>
@@ -1367,8 +1393,8 @@
       <c r="B16" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="16" t="s">
-        <v>83</v>
+      <c r="C16" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>64</v>
@@ -1384,8 +1410,8 @@
       <c r="B17" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C17" s="16" t="s">
-        <v>84</v>
+      <c r="C17" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>64</v>
@@ -1401,8 +1427,8 @@
       <c r="B18" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>85</v>
+      <c r="C18" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>64</v>
@@ -1418,8 +1444,8 @@
       <c r="B19" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>86</v>
+      <c r="C19" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>64</v>
@@ -1435,8 +1461,8 @@
       <c r="B20" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>87</v>
+      <c r="C20" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>64</v>
@@ -1452,8 +1478,8 @@
       <c r="B21" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>88</v>
+      <c r="C21" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>64</v>
@@ -1469,8 +1495,8 @@
       <c r="B22" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>89</v>
+      <c r="C22" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>64</v>
@@ -1486,8 +1512,8 @@
       <c r="B23" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>90</v>
+      <c r="C23" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>64</v>
@@ -1503,8 +1529,8 @@
       <c r="B24" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>91</v>
+      <c r="C24" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>64</v>
@@ -1520,8 +1546,8 @@
       <c r="B25" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>92</v>
+      <c r="C25" s="12" t="s">
+        <v>90</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>64</v>
@@ -1537,8 +1563,8 @@
       <c r="B26" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>93</v>
+      <c r="C26" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>64</v>
@@ -1554,8 +1580,8 @@
       <c r="B27" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>94</v>
+      <c r="C27" s="12" t="s">
+        <v>92</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>64</v>
@@ -1571,8 +1597,8 @@
       <c r="B28" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>95</v>
+      <c r="C28" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>64</v>
@@ -1588,8 +1614,8 @@
       <c r="B29" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C29" s="16" t="s">
-        <v>96</v>
+      <c r="C29" s="12" t="s">
+        <v>94</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>64</v>
@@ -1605,8 +1631,8 @@
       <c r="B30" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>97</v>
+      <c r="C30" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>64</v>
@@ -1622,8 +1648,8 @@
       <c r="B31" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C31" s="16" t="s">
-        <v>98</v>
+      <c r="C31" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>64</v>
@@ -1639,8 +1665,8 @@
       <c r="B32" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C32" s="16" t="s">
-        <v>99</v>
+      <c r="C32" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>64</v>
@@ -1656,8 +1682,8 @@
       <c r="B33" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>100</v>
+      <c r="C33" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>64</v>
@@ -1673,8 +1699,8 @@
       <c r="B34" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C34" s="16" t="s">
-        <v>101</v>
+      <c r="C34" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>64</v>
@@ -1690,8 +1716,8 @@
       <c r="B35" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C35" s="16" t="s">
-        <v>102</v>
+      <c r="C35" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>64</v>
@@ -1707,8 +1733,8 @@
       <c r="B36" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C36" s="16" t="s">
-        <v>103</v>
+      <c r="C36" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>64</v>
@@ -1724,8 +1750,8 @@
       <c r="B37" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>104</v>
+      <c r="C37" s="12" t="s">
+        <v>102</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>64</v>
@@ -1741,8 +1767,8 @@
       <c r="B38" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C38" s="16" t="s">
-        <v>105</v>
+      <c r="C38" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>64</v>
@@ -1758,8 +1784,8 @@
       <c r="B39" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C39" s="16" t="s">
-        <v>106</v>
+      <c r="C39" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>64</v>
@@ -1775,8 +1801,8 @@
       <c r="B40" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C40" s="16" t="s">
-        <v>107</v>
+      <c r="C40" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>64</v>
@@ -1792,8 +1818,8 @@
       <c r="B41" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>108</v>
+      <c r="C41" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>64</v>
@@ -1809,8 +1835,8 @@
       <c r="B42" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>109</v>
+      <c r="C42" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>64</v>
@@ -1826,8 +1852,8 @@
       <c r="B43" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C43" s="16" t="s">
-        <v>110</v>
+      <c r="C43" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>64</v>
@@ -1843,8 +1869,8 @@
       <c r="B44" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C44" s="16" t="s">
-        <v>111</v>
+      <c r="C44" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>64</v>
@@ -1860,8 +1886,8 @@
       <c r="B45" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C45" s="16" t="s">
-        <v>112</v>
+      <c r="C45" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>64</v>
@@ -1877,8 +1903,8 @@
       <c r="B46" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C46" s="16" t="s">
-        <v>113</v>
+      <c r="C46" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>64</v>
@@ -1894,8 +1920,8 @@
       <c r="B47" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C47" s="16" t="s">
-        <v>114</v>
+      <c r="C47" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>64</v>
@@ -1911,8 +1937,8 @@
       <c r="B48" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C48" s="16" t="s">
-        <v>115</v>
+      <c r="C48" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>64</v>
@@ -1928,8 +1954,8 @@
       <c r="B49" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C49" s="16" t="s">
-        <v>116</v>
+      <c r="C49" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>64</v>
@@ -1945,8 +1971,8 @@
       <c r="B50" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C50" s="16" t="s">
-        <v>117</v>
+      <c r="C50" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>64</v>
@@ -1962,8 +1988,8 @@
       <c r="B51" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C51" s="16" t="s">
-        <v>118</v>
+      <c r="C51" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>64</v>
@@ -1979,8 +2005,8 @@
       <c r="B52" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C52" s="16" t="s">
-        <v>119</v>
+      <c r="C52" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>64</v>
@@ -1996,8 +2022,8 @@
       <c r="B53" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C53" s="16" t="s">
-        <v>120</v>
+      <c r="C53" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>64</v>
@@ -2013,8 +2039,8 @@
       <c r="B54" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C54" s="16" t="s">
-        <v>121</v>
+      <c r="C54" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>64</v>
@@ -2030,8 +2056,8 @@
       <c r="B55" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C55" s="16" t="s">
-        <v>122</v>
+      <c r="C55" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>64</v>
@@ -2047,8 +2073,8 @@
       <c r="B56" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C56" s="16" t="s">
-        <v>123</v>
+      <c r="C56" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>64</v>
@@ -2064,8 +2090,8 @@
       <c r="B57" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C57" s="16" t="s">
-        <v>124</v>
+      <c r="C57" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>64</v>
@@ -2081,8 +2107,8 @@
       <c r="B58" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C58" s="16" t="s">
-        <v>125</v>
+      <c r="C58" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>64</v>
@@ -2098,8 +2124,8 @@
       <c r="B59" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C59" s="16" t="s">
-        <v>126</v>
+      <c r="C59" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>64</v>
@@ -2115,8 +2141,8 @@
       <c r="B60" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C60" s="16" t="s">
-        <v>127</v>
+      <c r="C60" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>64</v>
@@ -2132,8 +2158,8 @@
       <c r="B61" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C61" s="16" t="s">
-        <v>128</v>
+      <c r="C61" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>64</v>
@@ -2149,8 +2175,8 @@
       <c r="B62" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C62" s="16" t="s">
-        <v>129</v>
+      <c r="C62" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>64</v>
@@ -2166,8 +2192,8 @@
       <c r="B63" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C63" s="16" t="s">
-        <v>130</v>
+      <c r="C63" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>64</v>
@@ -2183,8 +2209,8 @@
       <c r="B64" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C64" s="16" t="s">
-        <v>131</v>
+      <c r="C64" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>64</v>
@@ -2200,8 +2226,8 @@
       <c r="B65" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C65" s="16" t="s">
-        <v>132</v>
+      <c r="C65" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>64</v>
@@ -2217,8 +2243,8 @@
       <c r="B66" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C66" s="16" t="s">
-        <v>133</v>
+      <c r="C66" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>64</v>
@@ -2234,8 +2260,8 @@
       <c r="B67" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C67" s="16" t="s">
-        <v>134</v>
+      <c r="C67" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>64</v>
@@ -2251,8 +2277,8 @@
       <c r="B68" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C68" s="16" t="s">
-        <v>135</v>
+      <c r="C68" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>64</v>
@@ -2268,8 +2294,8 @@
       <c r="B69" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C69" s="16" t="s">
-        <v>136</v>
+      <c r="C69" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>64</v>
@@ -2285,8 +2311,8 @@
       <c r="B70" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C70" s="16" t="s">
-        <v>137</v>
+      <c r="C70" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>64</v>
@@ -2302,8 +2328,8 @@
       <c r="B71" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C71" s="16" t="s">
-        <v>138</v>
+      <c r="C71" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>64</v>
@@ -2319,8 +2345,8 @@
       <c r="B72" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C72" s="16" t="s">
-        <v>139</v>
+      <c r="C72" s="12" t="s">
+        <v>137</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>64</v>
@@ -2328,7 +2354,6 @@
       <c r="E72" s="10">
         <v>1</v>
       </c>
-      <c r="F72" s="14"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" s="7" t="s">
@@ -2337,8 +2362,8 @@
       <c r="B73" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C73" s="16" t="s">
-        <v>140</v>
+      <c r="C73" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>64</v>
@@ -2354,8 +2379,8 @@
       <c r="B74" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C74" s="16" t="s">
-        <v>141</v>
+      <c r="C74" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>64</v>
@@ -2363,6 +2388,7 @@
       <c r="E74" s="10">
         <v>1</v>
       </c>
+      <c r="F74" s="14"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" s="7" t="s">
@@ -2371,8 +2397,8 @@
       <c r="B75" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C75" s="16" t="s">
-        <v>142</v>
+      <c r="C75" s="12" t="s">
+        <v>140</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>64</v>
@@ -2388,8 +2414,8 @@
       <c r="B76" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C76" s="16" t="s">
-        <v>143</v>
+      <c r="C76" s="12" t="s">
+        <v>141</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>64</v>
@@ -2405,8 +2431,8 @@
       <c r="B77" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C77" s="16" t="s">
-        <v>144</v>
+      <c r="C77" s="12" t="s">
+        <v>142</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>64</v>
@@ -2422,8 +2448,8 @@
       <c r="B78" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C78" s="16" t="s">
-        <v>145</v>
+      <c r="C78" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>64</v>
@@ -2439,8 +2465,8 @@
       <c r="B79" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C79" s="16" t="s">
-        <v>146</v>
+      <c r="C79" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>64</v>
@@ -2456,8 +2482,8 @@
       <c r="B80" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C80" s="16" t="s">
-        <v>147</v>
+      <c r="C80" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>64</v>
@@ -2473,8 +2499,8 @@
       <c r="B81" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C81" s="16" t="s">
-        <v>148</v>
+      <c r="C81" s="12" t="s">
+        <v>146</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>64</v>
@@ -2490,8 +2516,8 @@
       <c r="B82" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C82" s="16" t="s">
-        <v>149</v>
+      <c r="C82" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>64</v>
@@ -2507,8 +2533,8 @@
       <c r="B83" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C83" s="16" t="s">
-        <v>150</v>
+      <c r="C83" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>64</v>
@@ -2524,8 +2550,8 @@
       <c r="B84" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C84" s="16" t="s">
-        <v>151</v>
+      <c r="C84" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>64</v>
@@ -2541,8 +2567,8 @@
       <c r="B85" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C85" s="16" t="s">
-        <v>152</v>
+      <c r="C85" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>64</v>
@@ -2558,8 +2584,8 @@
       <c r="B86" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C86" s="16" t="s">
-        <v>153</v>
+      <c r="C86" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>64</v>
@@ -2575,8 +2601,8 @@
       <c r="B87" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C87" s="16" t="s">
-        <v>154</v>
+      <c r="C87" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>64</v>
@@ -2592,8 +2618,8 @@
       <c r="B88" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C88" s="16" t="s">
-        <v>155</v>
+      <c r="C88" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>64</v>
@@ -2609,8 +2635,8 @@
       <c r="B89" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C89" s="16" t="s">
-        <v>156</v>
+      <c r="C89" s="12" t="s">
+        <v>154</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>64</v>
@@ -2626,8 +2652,8 @@
       <c r="B90" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C90" s="16" t="s">
-        <v>157</v>
+      <c r="C90" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>64</v>
@@ -2643,8 +2669,8 @@
       <c r="B91" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C91" s="16" t="s">
-        <v>158</v>
+      <c r="C91" s="12" t="s">
+        <v>156</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>64</v>
@@ -2660,8 +2686,8 @@
       <c r="B92" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C92" s="16" t="s">
-        <v>159</v>
+      <c r="C92" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>64</v>
@@ -2677,8 +2703,8 @@
       <c r="B93" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C93" s="16" t="s">
-        <v>160</v>
+      <c r="C93" s="12" t="s">
+        <v>158</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>64</v>
@@ -2694,8 +2720,8 @@
       <c r="B94" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C94" s="16" t="s">
-        <v>161</v>
+      <c r="C94" s="12" t="s">
+        <v>159</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>64</v>
@@ -2711,8 +2737,8 @@
       <c r="B95" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C95" s="16" t="s">
-        <v>162</v>
+      <c r="C95" s="12" t="s">
+        <v>160</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>64</v>
@@ -2728,8 +2754,8 @@
       <c r="B96" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C96" s="16" t="s">
-        <v>163</v>
+      <c r="C96" s="12" t="s">
+        <v>161</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>64</v>
@@ -2745,8 +2771,8 @@
       <c r="B97" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C97" s="16" t="s">
-        <v>164</v>
+      <c r="C97" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>64</v>
@@ -2762,8 +2788,8 @@
       <c r="B98" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C98" s="16" t="s">
-        <v>165</v>
+      <c r="C98" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>64</v>
@@ -2779,8 +2805,8 @@
       <c r="B99" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C99" s="16" t="s">
-        <v>166</v>
+      <c r="C99" s="12" t="s">
+        <v>164</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>64</v>
@@ -2796,8 +2822,8 @@
       <c r="B100" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C100" s="16" t="s">
-        <v>167</v>
+      <c r="C100" s="12" t="s">
+        <v>165</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>64</v>
@@ -2813,8 +2839,8 @@
       <c r="B101" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C101" s="16" t="s">
-        <v>168</v>
+      <c r="C101" s="12" t="s">
+        <v>166</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>64</v>
@@ -2830,8 +2856,8 @@
       <c r="B102" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C102" s="16" t="s">
-        <v>169</v>
+      <c r="C102" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>64</v>
@@ -2847,8 +2873,8 @@
       <c r="B103" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C103" s="16" t="s">
-        <v>170</v>
+      <c r="C103" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>64</v>
@@ -2864,8 +2890,8 @@
       <c r="B104" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C104" s="16" t="s">
-        <v>171</v>
+      <c r="C104" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>64</v>
@@ -2881,8 +2907,8 @@
       <c r="B105" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C105" s="16" t="s">
-        <v>172</v>
+      <c r="C105" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>64</v>
@@ -2898,8 +2924,8 @@
       <c r="B106" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="16" t="s">
-        <v>173</v>
+      <c r="C106" s="12" t="s">
+        <v>171</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>64</v>
@@ -2915,8 +2941,8 @@
       <c r="B107" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C107" s="16" t="s">
-        <v>174</v>
+      <c r="C107" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>64</v>
@@ -2932,8 +2958,8 @@
       <c r="B108" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C108" s="16" t="s">
-        <v>175</v>
+      <c r="C108" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>64</v>
@@ -2944,16 +2970,16 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A109" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>176</v>
+        <v>218</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E109" s="10">
         <v>1</v>
@@ -2961,16 +2987,16 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A110" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>177</v>
+        <v>218</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E110" s="10">
         <v>1</v>
@@ -2983,8 +3009,8 @@
       <c r="B111" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>178</v>
+      <c r="C111" s="18" t="s">
+        <v>177</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>65</v>
@@ -3000,8 +3026,8 @@
       <c r="B112" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>179</v>
+      <c r="C112" s="18" t="s">
+        <v>178</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>65</v>
@@ -3017,8 +3043,8 @@
       <c r="B113" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>180</v>
+      <c r="C113" s="18" t="s">
+        <v>179</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>65</v>
@@ -3034,8 +3060,8 @@
       <c r="B114" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>181</v>
+      <c r="C114" s="18" t="s">
+        <v>180</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>65</v>
@@ -3051,8 +3077,8 @@
       <c r="B115" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C115" s="10" t="s">
-        <v>182</v>
+      <c r="C115" s="18" t="s">
+        <v>181</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>65</v>
@@ -3068,8 +3094,8 @@
       <c r="B116" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>183</v>
+      <c r="C116" s="18" t="s">
+        <v>182</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>65</v>
@@ -3085,8 +3111,8 @@
       <c r="B117" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C117" s="10" t="s">
-        <v>184</v>
+      <c r="C117" s="18" t="s">
+        <v>183</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>65</v>
@@ -3102,8 +3128,8 @@
       <c r="B118" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C118" s="10" t="s">
-        <v>185</v>
+      <c r="C118" s="18" t="s">
+        <v>184</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>65</v>
@@ -3119,8 +3145,8 @@
       <c r="B119" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C119" s="10" t="s">
-        <v>186</v>
+      <c r="C119" s="18" t="s">
+        <v>185</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>65</v>
@@ -3136,8 +3162,8 @@
       <c r="B120" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C120" s="10" t="s">
-        <v>187</v>
+      <c r="C120" s="18" t="s">
+        <v>186</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>65</v>
@@ -3153,8 +3179,8 @@
       <c r="B121" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C121" s="10" t="s">
-        <v>188</v>
+      <c r="C121" s="18" t="s">
+        <v>187</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>65</v>
@@ -3170,8 +3196,8 @@
       <c r="B122" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C122" s="10" t="s">
-        <v>189</v>
+      <c r="C122" s="18" t="s">
+        <v>188</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>65</v>
@@ -3187,8 +3213,8 @@
       <c r="B123" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C123" s="10" t="s">
-        <v>190</v>
+      <c r="C123" s="18" t="s">
+        <v>189</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>65</v>
@@ -3204,8 +3230,8 @@
       <c r="B124" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>191</v>
+      <c r="C124" s="18" t="s">
+        <v>190</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>65</v>
@@ -3221,8 +3247,8 @@
       <c r="B125" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>192</v>
+      <c r="C125" s="18" t="s">
+        <v>191</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>65</v>
@@ -3238,8 +3264,8 @@
       <c r="B126" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C126" s="10" t="s">
-        <v>193</v>
+      <c r="C126" s="18" t="s">
+        <v>192</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>65</v>
@@ -3255,8 +3281,8 @@
       <c r="B127" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C127" s="10" t="s">
-        <v>194</v>
+      <c r="C127" s="18" t="s">
+        <v>193</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>65</v>
@@ -3272,8 +3298,8 @@
       <c r="B128" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>195</v>
+      <c r="C128" s="18" t="s">
+        <v>194</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>65</v>
@@ -3289,8 +3315,8 @@
       <c r="B129" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C129" s="10" t="s">
-        <v>196</v>
+      <c r="C129" s="18" t="s">
+        <v>195</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>65</v>
@@ -3306,8 +3332,8 @@
       <c r="B130" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C130" s="10" t="s">
-        <v>197</v>
+      <c r="C130" s="18" t="s">
+        <v>196</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>65</v>
@@ -3318,16 +3344,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A131" s="7" t="s">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>55</v>
+        <v>213</v>
+      </c>
+      <c r="C131" s="18" t="s">
+        <v>197</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="E131" s="10">
         <v>1</v>
@@ -3335,12 +3361,12 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A132" s="7" t="s">
-        <v>5</v>
+        <v>202</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="17" t="s">
         <v>55</v>
       </c>
       <c r="D132" s="4" t="s">
@@ -3357,8 +3383,8 @@
       <c r="B133" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C133" s="4" t="s">
-        <v>203</v>
+      <c r="C133" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>210</v>
@@ -3374,8 +3400,8 @@
       <c r="B134" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C134" s="16" t="s">
-        <v>204</v>
+      <c r="C134" s="17" t="s">
+        <v>203</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>210</v>
@@ -3391,8 +3417,8 @@
       <c r="B135" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C135" s="16" t="s">
-        <v>205</v>
+      <c r="C135" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>210</v>
@@ -3408,8 +3434,8 @@
       <c r="B136" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C136" s="16" t="s">
-        <v>206</v>
+      <c r="C136" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>210</v>
@@ -3425,8 +3451,8 @@
       <c r="B137" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C137" s="16" t="s">
-        <v>207</v>
+      <c r="C137" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>210</v>
@@ -3437,29 +3463,29 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A138" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B138" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>201</v>
+        <v>5</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E138" s="14">
-        <v>271000000</v>
+      <c r="E138" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A139" s="7" t="s">
-        <v>5</v>
+        <v>202</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" s="17" t="s">
         <v>201</v>
       </c>
       <c r="D139" s="4" t="s">
@@ -3476,8 +3502,8 @@
       <c r="B140" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C140" s="4" t="s">
-        <v>203</v>
+      <c r="C140" s="17" t="s">
+        <v>201</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>210</v>
@@ -3493,8 +3519,8 @@
       <c r="B141" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C141" s="16" t="s">
-        <v>204</v>
+      <c r="C141" s="17" t="s">
+        <v>203</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>210</v>
@@ -3510,8 +3536,8 @@
       <c r="B142" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C142" s="16" t="s">
-        <v>205</v>
+      <c r="C142" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>210</v>
@@ -3527,8 +3553,8 @@
       <c r="B143" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C143" s="16" t="s">
-        <v>206</v>
+      <c r="C143" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>210</v>
@@ -3544,8 +3570,8 @@
       <c r="B144" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C144" s="16" t="s">
-        <v>207</v>
+      <c r="C144" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>210</v>
@@ -3556,40 +3582,39 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A145" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B145" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C145" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E145" s="14">
+        <v>271000000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A146" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C146" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="D145" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E145" s="10">
+      <c r="D146" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E146" s="10">
         <f>(1*0.95)*1000000</f>
         <v>950000</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A146" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B146" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="C146" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E146" s="10">
-        <f t="shared" ref="E146:E166" si="0">(1*0.88)*1000000</f>
-        <v>880000</v>
-      </c>
-    </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A147" s="7" t="s">
         <v>4</v>
@@ -3597,14 +3622,14 @@
       <c r="B147" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C147" s="10" t="s">
-        <v>178</v>
+      <c r="C147" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E147" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E147:E167" si="0">(1*0.88)*1000000</f>
         <v>880000</v>
       </c>
     </row>
@@ -3615,8 +3640,8 @@
       <c r="B148" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C148" s="10" t="s">
-        <v>179</v>
+      <c r="C148" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>65</v>
@@ -3633,8 +3658,8 @@
       <c r="B149" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C149" s="10" t="s">
-        <v>180</v>
+      <c r="C149" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>65</v>
@@ -3651,8 +3676,8 @@
       <c r="B150" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C150" s="10" t="s">
-        <v>181</v>
+      <c r="C150" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>65</v>
@@ -3669,8 +3694,8 @@
       <c r="B151" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C151" s="10" t="s">
-        <v>182</v>
+      <c r="C151" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>65</v>
@@ -3687,8 +3712,8 @@
       <c r="B152" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C152" s="10" t="s">
-        <v>183</v>
+      <c r="C152" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>65</v>
@@ -3705,8 +3730,8 @@
       <c r="B153" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C153" s="10" t="s">
-        <v>184</v>
+      <c r="C153" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>65</v>
@@ -3723,8 +3748,8 @@
       <c r="B154" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C154" s="10" t="s">
-        <v>185</v>
+      <c r="C154" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>65</v>
@@ -3741,8 +3766,8 @@
       <c r="B155" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C155" s="10" t="s">
-        <v>186</v>
+      <c r="C155" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>65</v>
@@ -3759,8 +3784,8 @@
       <c r="B156" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C156" s="10" t="s">
-        <v>187</v>
+      <c r="C156" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>65</v>
@@ -3777,8 +3802,8 @@
       <c r="B157" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C157" s="10" t="s">
-        <v>188</v>
+      <c r="C157" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>65</v>
@@ -3795,8 +3820,8 @@
       <c r="B158" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C158" s="10" t="s">
-        <v>189</v>
+      <c r="C158" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>65</v>
@@ -3813,8 +3838,8 @@
       <c r="B159" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C159" s="10" t="s">
-        <v>190</v>
+      <c r="C159" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>65</v>
@@ -3831,8 +3856,8 @@
       <c r="B160" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C160" s="10" t="s">
-        <v>191</v>
+      <c r="C160" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>65</v>
@@ -3849,8 +3874,8 @@
       <c r="B161" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C161" s="10" t="s">
-        <v>192</v>
+      <c r="C161" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>65</v>
@@ -3867,8 +3892,8 @@
       <c r="B162" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C162" s="10" t="s">
-        <v>193</v>
+      <c r="C162" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>65</v>
@@ -3885,8 +3910,8 @@
       <c r="B163" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C163" s="10" t="s">
-        <v>194</v>
+      <c r="C163" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>65</v>
@@ -3903,8 +3928,8 @@
       <c r="B164" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C164" s="10" t="s">
-        <v>195</v>
+      <c r="C164" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>65</v>
@@ -3921,8 +3946,8 @@
       <c r="B165" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C165" s="10" t="s">
-        <v>196</v>
+      <c r="C165" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>65</v>
@@ -3939,8 +3964,8 @@
       <c r="B166" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C166" s="10" t="s">
-        <v>197</v>
+      <c r="C166" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>65</v>
@@ -3957,35 +3982,35 @@
       <c r="B167" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="C167" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E167" s="10">
+        <f t="shared" si="0"/>
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A168" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D167" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E167" s="10">
+      <c r="D168" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E168" s="10">
         <f>(1*0.17)*1000000</f>
         <v>170000</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A168" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B168" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="C168" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E168" s="10">
-        <f t="shared" ref="E168:E170" si="1">(1*0.4)*1000000</f>
-        <v>400000</v>
-      </c>
-    </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A169" s="7" t="s">
         <v>4</v>
@@ -3993,49 +4018,67 @@
       <c r="B169" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C169" s="10" t="s">
+      <c r="C169" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E169" s="10">
+        <f t="shared" ref="E169:E171" si="1">(1*0.4)*1000000</f>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A170" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D169" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E169" s="10">
+      <c r="D170" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E170" s="10">
         <f>(1*0.4)*1000000</f>
         <v>400000</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A170" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B170" s="11" t="s">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A171" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B171" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C170" s="10" t="s">
+      <c r="C171" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D170" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E170" s="10">
+      <c r="D171" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E171" s="10">
         <f t="shared" si="1"/>
         <v>400000</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A171" s="11" t="s">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A172" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="B171" s="11" t="s">
+      <c r="B172" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="C172" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="D172" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E171" s="10">
+      <c r="E172" s="10">
         <v>1</v>
       </c>
     </row>

--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CDE311-0258-4555-BAA6-F1A503B05757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF57980F-9BA4-470B-B839-C6A7DB36E002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="synthèse" sheetId="5" r:id="rId1"/>
@@ -1121,17 +1121,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D0163B-5317-4028-ABDC-4C843EF1CC69}">
   <dimension ref="A1:F172"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.69140625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" style="10" customWidth="1"/>
     <col min="2" max="2" width="17" style="10" customWidth="1"/>
-    <col min="3" max="3" width="47.84375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="47.86328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="10" customWidth="1"/>
-    <col min="5" max="5" width="13.23046875" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="9.23046875" style="10"/>
+    <col min="5" max="5" width="13.19921875" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9.19921875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="38" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="14.85" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>8.2400000000000005E-10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>6.3599999999999998E-10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
         <v>2</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>3.0399999999999998E-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>2</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>3E-10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="9" t="s">
         <v>2</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>3E-10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
         <v>3</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
         <v>3</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="s">
         <v>3</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
         <v>3</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
         <v>3</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="s">
         <v>3</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
         <v>3</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
         <v>3</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="s">
         <v>3</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
         <v>3</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
         <v>3</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="s">
         <v>3</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="s">
         <v>3</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
         <v>3</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
         <v>3</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="s">
         <v>3</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
         <v>3</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
         <v>3</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="s">
         <v>3</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
         <v>3</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
         <v>3</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="7" t="s">
         <v>3</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
         <v>3</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
         <v>3</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
         <v>3</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
         <v>3</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="7" t="s">
         <v>3</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="7" t="s">
         <v>3</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
         <v>3</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
         <v>3</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
         <v>3</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="7" t="s">
         <v>3</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="7" t="s">
         <v>3</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="7" t="s">
         <v>3</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="7" t="s">
         <v>3</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
         <v>3</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
         <v>3</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
         <v>3</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="7" t="s">
         <v>3</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="7" t="s">
         <v>3</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
         <v>3</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="7" t="s">
         <v>3</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="7" t="s">
         <v>3</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="7" t="s">
         <v>3</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="7" t="s">
         <v>3</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="7" t="s">
         <v>3</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="7" t="s">
         <v>3</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="7" t="s">
         <v>3</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="7" t="s">
         <v>3</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" s="7" t="s">
         <v>3</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="7" t="s">
         <v>3</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="7" t="s">
         <v>3</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="7" t="s">
         <v>3</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="7" t="s">
         <v>3</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="7" t="s">
         <v>3</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="7" t="s">
         <v>3</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" s="7" t="s">
         <v>3</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" s="7" t="s">
         <v>3</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" s="7" t="s">
         <v>3</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" s="7" t="s">
         <v>3</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="7" t="s">
         <v>3</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" s="7" t="s">
         <v>3</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="7" t="s">
         <v>3</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" s="7" t="s">
         <v>3</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" s="7" t="s">
         <v>3</v>
       </c>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="F74" s="14"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" s="7" t="s">
         <v>3</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" s="7" t="s">
         <v>3</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" s="7" t="s">
         <v>3</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" s="7" t="s">
         <v>3</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="7" t="s">
         <v>3</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="7" t="s">
         <v>3</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="7" t="s">
         <v>3</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="7" t="s">
         <v>3</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="7" t="s">
         <v>3</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="7" t="s">
         <v>3</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="7" t="s">
         <v>3</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="7" t="s">
         <v>3</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="7" t="s">
         <v>3</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="7" t="s">
         <v>3</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="7" t="s">
         <v>3</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="7" t="s">
         <v>3</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="7" t="s">
         <v>3</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="7" t="s">
         <v>3</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="7" t="s">
         <v>3</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" s="7" t="s">
         <v>3</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" s="7" t="s">
         <v>3</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" s="7" t="s">
         <v>3</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="7" t="s">
         <v>3</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="7" t="s">
         <v>3</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="7" t="s">
         <v>3</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="7" t="s">
         <v>3</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="7" t="s">
         <v>3</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="7" t="s">
         <v>3</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="7" t="s">
         <v>3</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="7" t="s">
         <v>3</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="7" t="s">
         <v>3</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="7" t="s">
         <v>3</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="7" t="s">
         <v>3</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="7" t="s">
         <v>3</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="7" t="s">
         <v>3</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="7" t="s">
         <v>3</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="7" t="s">
         <v>4</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" s="7" t="s">
         <v>4</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="7" t="s">
         <v>4</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="7" t="s">
         <v>4</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="7" t="s">
         <v>4</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="7" t="s">
         <v>4</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="7" t="s">
         <v>4</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="7" t="s">
         <v>4</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="7" t="s">
         <v>4</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="7" t="s">
         <v>4</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="7" t="s">
         <v>4</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="7" t="s">
         <v>4</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="7" t="s">
         <v>4</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="7" t="s">
         <v>4</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="7" t="s">
         <v>4</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="7" t="s">
         <v>4</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="7" t="s">
         <v>4</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="7" t="s">
         <v>4</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="7" t="s">
         <v>4</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="7" t="s">
         <v>4</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="7" t="s">
         <v>4</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="7" t="s">
         <v>202</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="7" t="s">
         <v>5</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="7" t="s">
         <v>5</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="7" t="s">
         <v>5</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="7" t="s">
         <v>5</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="7" t="s">
         <v>5</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="7" t="s">
         <v>5</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="7" t="s">
         <v>202</v>
       </c>
@@ -3492,10 +3492,11 @@
         <v>210</v>
       </c>
       <c r="E139" s="14">
-        <v>271000000</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.4">
+        <f>4.37*0.00001*1000000000</f>
+        <v>43700.000000000007</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="7" t="s">
         <v>5</v>
       </c>
@@ -3509,10 +3510,11 @@
         <v>210</v>
       </c>
       <c r="E140" s="14">
-        <v>271000000</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" ref="E140:E145" si="0">4.37*0.00001*1000000000</f>
+        <v>43700.000000000007</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" s="7" t="s">
         <v>5</v>
       </c>
@@ -3526,10 +3528,11 @@
         <v>210</v>
       </c>
       <c r="E141" s="14">
-        <v>271000000</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>43700.000000000007</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" s="7" t="s">
         <v>5</v>
       </c>
@@ -3543,10 +3546,11 @@
         <v>210</v>
       </c>
       <c r="E142" s="14">
-        <v>271000000</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>43700.000000000007</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="7" t="s">
         <v>5</v>
       </c>
@@ -3560,10 +3564,11 @@
         <v>210</v>
       </c>
       <c r="E143" s="14">
-        <v>271000000</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>43700.000000000007</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="7" t="s">
         <v>5</v>
       </c>
@@ -3577,10 +3582,11 @@
         <v>210</v>
       </c>
       <c r="E144" s="14">
-        <v>271000000</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>43700.000000000007</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="7" t="s">
         <v>5</v>
       </c>
@@ -3594,10 +3600,11 @@
         <v>210</v>
       </c>
       <c r="E145" s="14">
-        <v>271000000</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>43700.000000000007</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="7" t="s">
         <v>4</v>
       </c>
@@ -3611,11 +3618,11 @@
         <v>65</v>
       </c>
       <c r="E146" s="10">
-        <f>(1*0.95)*1000000</f>
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.4">
+        <f>0.95*100</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="7" t="s">
         <v>4</v>
       </c>
@@ -3629,11 +3636,11 @@
         <v>65</v>
       </c>
       <c r="E147" s="10">
-        <f t="shared" ref="E147:E167" si="0">(1*0.88)*1000000</f>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.4">
+        <f>0.88*100</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="7" t="s">
         <v>4</v>
       </c>
@@ -3647,11 +3654,11 @@
         <v>65</v>
       </c>
       <c r="E148" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" ref="E148:E167" si="1">0.88*100</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" s="7" t="s">
         <v>4</v>
       </c>
@@ -3665,11 +3672,11 @@
         <v>65</v>
       </c>
       <c r="E149" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" s="7" t="s">
         <v>4</v>
       </c>
@@ -3683,11 +3690,11 @@
         <v>65</v>
       </c>
       <c r="E150" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" s="7" t="s">
         <v>4</v>
       </c>
@@ -3701,11 +3708,11 @@
         <v>65</v>
       </c>
       <c r="E151" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" s="7" t="s">
         <v>4</v>
       </c>
@@ -3719,11 +3726,11 @@
         <v>65</v>
       </c>
       <c r="E152" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="7" t="s">
         <v>4</v>
       </c>
@@ -3737,11 +3744,11 @@
         <v>65</v>
       </c>
       <c r="E153" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" s="7" t="s">
         <v>4</v>
       </c>
@@ -3755,11 +3762,11 @@
         <v>65</v>
       </c>
       <c r="E154" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="7" t="s">
         <v>4</v>
       </c>
@@ -3773,11 +3780,11 @@
         <v>65</v>
       </c>
       <c r="E155" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" s="7" t="s">
         <v>4</v>
       </c>
@@ -3791,11 +3798,11 @@
         <v>65</v>
       </c>
       <c r="E156" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="7" t="s">
         <v>4</v>
       </c>
@@ -3809,11 +3816,11 @@
         <v>65</v>
       </c>
       <c r="E157" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="7" t="s">
         <v>4</v>
       </c>
@@ -3827,11 +3834,11 @@
         <v>65</v>
       </c>
       <c r="E158" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" s="7" t="s">
         <v>4</v>
       </c>
@@ -3845,11 +3852,11 @@
         <v>65</v>
       </c>
       <c r="E159" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" s="7" t="s">
         <v>4</v>
       </c>
@@ -3863,11 +3870,11 @@
         <v>65</v>
       </c>
       <c r="E160" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" s="7" t="s">
         <v>4</v>
       </c>
@@ -3881,11 +3888,11 @@
         <v>65</v>
       </c>
       <c r="E161" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" s="7" t="s">
         <v>4</v>
       </c>
@@ -3899,11 +3906,11 @@
         <v>65</v>
       </c>
       <c r="E162" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" s="7" t="s">
         <v>4</v>
       </c>
@@ -3917,11 +3924,11 @@
         <v>65</v>
       </c>
       <c r="E163" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" s="7" t="s">
         <v>4</v>
       </c>
@@ -3935,11 +3942,11 @@
         <v>65</v>
       </c>
       <c r="E164" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" s="7" t="s">
         <v>4</v>
       </c>
@@ -3953,11 +3960,11 @@
         <v>65</v>
       </c>
       <c r="E165" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" s="7" t="s">
         <v>4</v>
       </c>
@@ -3971,11 +3978,11 @@
         <v>65</v>
       </c>
       <c r="E166" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" s="7" t="s">
         <v>4</v>
       </c>
@@ -3989,11 +3996,11 @@
         <v>65</v>
       </c>
       <c r="E167" s="10">
-        <f t="shared" si="0"/>
-        <v>880000</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168" s="7" t="s">
         <v>4</v>
       </c>
@@ -4007,11 +4014,11 @@
         <v>65</v>
       </c>
       <c r="E168" s="10">
-        <f>(1*0.17)*1000000</f>
-        <v>170000</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.4">
+        <f>0.17*100</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" s="7" t="s">
         <v>4</v>
       </c>
@@ -4025,11 +4032,11 @@
         <v>65</v>
       </c>
       <c r="E169" s="10">
-        <f t="shared" ref="E169:E171" si="1">(1*0.4)*1000000</f>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.4">
+        <f>0.4*100</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" s="7" t="s">
         <v>4</v>
       </c>
@@ -4043,11 +4050,11 @@
         <v>65</v>
       </c>
       <c r="E170" s="10">
-        <f>(1*0.4)*1000000</f>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" ref="E170:E171" si="2">0.4*100</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" s="7" t="s">
         <v>4</v>
       </c>
@@ -4061,11 +4068,11 @@
         <v>65</v>
       </c>
       <c r="E171" s="10">
-        <f t="shared" si="1"/>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
         <v>208</v>
       </c>
@@ -4091,17 +4098,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDE2010-B659-4D8C-A3CE-548591F6AB6A}">
   <dimension ref="A1:F207"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.69140625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" style="10" customWidth="1"/>
     <col min="2" max="2" width="17" style="10" customWidth="1"/>
-    <col min="3" max="3" width="47.84375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="47.86328125" style="10" customWidth="1"/>
     <col min="4" max="4" width="9" style="10" customWidth="1"/>
-    <col min="5" max="5" width="13.23046875" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="9.23046875" style="10"/>
+    <col min="5" max="5" width="13.19921875" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9.19921875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="38" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -4118,7 +4125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="14.85" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
@@ -4135,7 +4142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -4152,7 +4159,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -4169,7 +4176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
         <v>2</v>
       </c>
@@ -4186,7 +4193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>2</v>
       </c>
@@ -4203,7 +4210,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -4220,7 +4227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
         <v>3</v>
       </c>
@@ -4237,7 +4244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
         <v>3</v>
       </c>
@@ -4254,7 +4261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -4271,7 +4278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="s">
         <v>3</v>
       </c>
@@ -4288,7 +4295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
         <v>3</v>
       </c>
@@ -4305,7 +4312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
         <v>3</v>
       </c>
@@ -4322,7 +4329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="s">
         <v>3</v>
       </c>
@@ -4339,7 +4346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
         <v>3</v>
       </c>
@@ -4356,7 +4363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
         <v>3</v>
       </c>
@@ -4373,7 +4380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="s">
         <v>3</v>
       </c>
@@ -4390,7 +4397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
         <v>3</v>
       </c>
@@ -4407,7 +4414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
         <v>3</v>
       </c>
@@ -4424,7 +4431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="s">
         <v>3</v>
       </c>
@@ -4441,7 +4448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="s">
         <v>3</v>
       </c>
@@ -4458,7 +4465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
         <v>3</v>
       </c>
@@ -4475,7 +4482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
         <v>3</v>
       </c>
@@ -4492,7 +4499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="s">
         <v>3</v>
       </c>
@@ -4509,7 +4516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
         <v>3</v>
       </c>
@@ -4526,7 +4533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
         <v>3</v>
       </c>
@@ -4543,7 +4550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="s">
         <v>3</v>
       </c>
@@ -4560,7 +4567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
         <v>3</v>
       </c>
@@ -4577,7 +4584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
         <v>3</v>
       </c>
@@ -4594,7 +4601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
@@ -4611,7 +4618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="7" t="s">
         <v>3</v>
       </c>
@@ -4628,7 +4635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
         <v>3</v>
       </c>
@@ -4645,7 +4652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
         <v>3</v>
       </c>
@@ -4662,7 +4669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
         <v>3</v>
       </c>
@@ -4679,7 +4686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
         <v>3</v>
       </c>
@@ -4696,7 +4703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="7" t="s">
         <v>3</v>
       </c>
@@ -4713,7 +4720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="7" t="s">
         <v>3</v>
       </c>
@@ -4730,7 +4737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
         <v>3</v>
       </c>
@@ -4747,7 +4754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
         <v>3</v>
       </c>
@@ -4764,7 +4771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
         <v>3</v>
       </c>
@@ -4781,7 +4788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="7" t="s">
         <v>3</v>
       </c>
@@ -4798,7 +4805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="7" t="s">
         <v>3</v>
       </c>
@@ -4815,7 +4822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="7" t="s">
         <v>3</v>
       </c>
@@ -4832,7 +4839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="7" t="s">
         <v>3</v>
       </c>
@@ -4849,7 +4856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
         <v>3</v>
       </c>
@@ -4866,7 +4873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
         <v>3</v>
       </c>
@@ -4883,7 +4890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
         <v>3</v>
       </c>
@@ -4900,7 +4907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="7" t="s">
         <v>3</v>
       </c>
@@ -4917,7 +4924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="7" t="s">
         <v>3</v>
       </c>
@@ -4934,7 +4941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
         <v>3</v>
       </c>
@@ -4951,7 +4958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="7" t="s">
         <v>3</v>
       </c>
@@ -4968,7 +4975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="7" t="s">
         <v>3</v>
       </c>
@@ -4985,7 +4992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="7" t="s">
         <v>3</v>
       </c>
@@ -5002,7 +5009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="7" t="s">
         <v>3</v>
       </c>
@@ -5019,7 +5026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="7" t="s">
         <v>3</v>
       </c>
@@ -5036,7 +5043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="7" t="s">
         <v>3</v>
       </c>
@@ -5053,7 +5060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="7" t="s">
         <v>3</v>
       </c>
@@ -5070,7 +5077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="7" t="s">
         <v>3</v>
       </c>
@@ -5087,7 +5094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" s="7" t="s">
         <v>3</v>
       </c>
@@ -5104,7 +5111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="7" t="s">
         <v>3</v>
       </c>
@@ -5121,7 +5128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="7" t="s">
         <v>3</v>
       </c>
@@ -5138,7 +5145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="7" t="s">
         <v>3</v>
       </c>
@@ -5155,7 +5162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="7" t="s">
         <v>3</v>
       </c>
@@ -5172,7 +5179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="7" t="s">
         <v>3</v>
       </c>
@@ -5189,7 +5196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="7" t="s">
         <v>3</v>
       </c>
@@ -5206,7 +5213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" s="7" t="s">
         <v>3</v>
       </c>
@@ -5223,7 +5230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" s="7" t="s">
         <v>3</v>
       </c>
@@ -5240,7 +5247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" s="7" t="s">
         <v>3</v>
       </c>
@@ -5257,7 +5264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" s="7" t="s">
         <v>3</v>
       </c>
@@ -5274,7 +5281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="7" t="s">
         <v>3</v>
       </c>
@@ -5291,7 +5298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" s="7" t="s">
         <v>3</v>
       </c>
@@ -5308,7 +5315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="7" t="s">
         <v>3</v>
       </c>
@@ -5325,7 +5332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" s="7" t="s">
         <v>3</v>
       </c>
@@ -5343,7 +5350,7 @@
       </c>
       <c r="F73" s="14"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" s="7" t="s">
         <v>3</v>
       </c>
@@ -5360,7 +5367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" s="7" t="s">
         <v>3</v>
       </c>
@@ -5377,7 +5384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" s="7" t="s">
         <v>3</v>
       </c>
@@ -5394,7 +5401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" s="7" t="s">
         <v>3</v>
       </c>
@@ -5411,7 +5418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" s="7" t="s">
         <v>3</v>
       </c>
@@ -5428,7 +5435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="7" t="s">
         <v>3</v>
       </c>
@@ -5445,7 +5452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="7" t="s">
         <v>3</v>
       </c>
@@ -5462,7 +5469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="7" t="s">
         <v>3</v>
       </c>
@@ -5479,7 +5486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="7" t="s">
         <v>3</v>
       </c>
@@ -5496,7 +5503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="7" t="s">
         <v>3</v>
       </c>
@@ -5513,7 +5520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="7" t="s">
         <v>3</v>
       </c>
@@ -5530,7 +5537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="7" t="s">
         <v>3</v>
       </c>
@@ -5547,7 +5554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="7" t="s">
         <v>3</v>
       </c>
@@ -5564,7 +5571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="7" t="s">
         <v>3</v>
       </c>
@@ -5581,7 +5588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="7" t="s">
         <v>3</v>
       </c>
@@ -5598,7 +5605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="7" t="s">
         <v>3</v>
       </c>
@@ -5615,7 +5622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="7" t="s">
         <v>3</v>
       </c>
@@ -5632,7 +5639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="7" t="s">
         <v>3</v>
       </c>
@@ -5649,7 +5656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="7" t="s">
         <v>3</v>
       </c>
@@ -5666,7 +5673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="7" t="s">
         <v>3</v>
       </c>
@@ -5683,7 +5690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" s="7" t="s">
         <v>3</v>
       </c>
@@ -5700,7 +5707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" s="7" t="s">
         <v>3</v>
       </c>
@@ -5717,7 +5724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" s="7" t="s">
         <v>3</v>
       </c>
@@ -5734,7 +5741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="7" t="s">
         <v>3</v>
       </c>
@@ -5751,7 +5758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="7" t="s">
         <v>3</v>
       </c>
@@ -5768,7 +5775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="7" t="s">
         <v>3</v>
       </c>
@@ -5785,7 +5792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="7" t="s">
         <v>3</v>
       </c>
@@ -5802,7 +5809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="7" t="s">
         <v>3</v>
       </c>
@@ -5819,7 +5826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="7" t="s">
         <v>3</v>
       </c>
@@ -5836,7 +5843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="7" t="s">
         <v>3</v>
       </c>
@@ -5853,7 +5860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="7" t="s">
         <v>3</v>
       </c>
@@ -5870,7 +5877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="7" t="s">
         <v>3</v>
       </c>
@@ -5887,7 +5894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="7" t="s">
         <v>3</v>
       </c>
@@ -5904,7 +5911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="7" t="s">
         <v>3</v>
       </c>
@@ -5921,7 +5928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="7" t="s">
         <v>3</v>
       </c>
@@ -5938,7 +5945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="7" t="s">
         <v>3</v>
       </c>
@@ -5955,7 +5962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="7" t="s">
         <v>4</v>
       </c>
@@ -5972,7 +5979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="7" t="s">
         <v>4</v>
       </c>
@@ -5989,7 +5996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" s="7" t="s">
         <v>4</v>
       </c>
@@ -6006,7 +6013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="7" t="s">
         <v>4</v>
       </c>
@@ -6023,7 +6030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="7" t="s">
         <v>4</v>
       </c>
@@ -6040,7 +6047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="7" t="s">
         <v>4</v>
       </c>
@@ -6057,7 +6064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="7" t="s">
         <v>4</v>
       </c>
@@ -6074,7 +6081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="7" t="s">
         <v>4</v>
       </c>
@@ -6091,7 +6098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="7" t="s">
         <v>4</v>
       </c>
@@ -6108,7 +6115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="7" t="s">
         <v>4</v>
       </c>
@@ -6125,7 +6132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="7" t="s">
         <v>4</v>
       </c>
@@ -6142,7 +6149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="7" t="s">
         <v>4</v>
       </c>
@@ -6159,7 +6166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="7" t="s">
         <v>4</v>
       </c>
@@ -6176,7 +6183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="7" t="s">
         <v>4</v>
       </c>
@@ -6193,7 +6200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="7" t="s">
         <v>4</v>
       </c>
@@ -6210,7 +6217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="7" t="s">
         <v>4</v>
       </c>
@@ -6227,7 +6234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="7" t="s">
         <v>4</v>
       </c>
@@ -6244,7 +6251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="7" t="s">
         <v>4</v>
       </c>
@@ -6261,7 +6268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="7" t="s">
         <v>4</v>
       </c>
@@ -6278,7 +6285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="7" t="s">
         <v>4</v>
       </c>
@@ -6295,7 +6302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="7" t="s">
         <v>4</v>
       </c>
@@ -6312,7 +6319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="7" t="s">
         <v>4</v>
       </c>
@@ -6329,7 +6336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="7" t="s">
         <v>5</v>
       </c>
@@ -6346,7 +6353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="7" t="s">
         <v>5</v>
       </c>
@@ -6363,7 +6370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="7" t="s">
         <v>5</v>
       </c>
@@ -6380,7 +6387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="7" t="s">
         <v>5</v>
       </c>
@@ -6397,7 +6404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="7" t="s">
         <v>5</v>
       </c>
@@ -6414,7 +6421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="7" t="s">
         <v>5</v>
       </c>
@@ -6431,7 +6438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="7" t="s">
         <v>5</v>
       </c>
@@ -6448,7 +6455,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="7" t="s">
         <v>5</v>
       </c>
@@ -6465,7 +6472,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="7" t="s">
         <v>5</v>
       </c>
@@ -6482,7 +6489,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" s="7" t="s">
         <v>5</v>
       </c>
@@ -6499,7 +6506,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" s="7" t="s">
         <v>5</v>
       </c>
@@ -6516,7 +6523,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="7" t="s">
         <v>5</v>
       </c>
@@ -6533,7 +6540,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="7" t="s">
         <v>5</v>
       </c>
@@ -6550,7 +6557,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="7" t="s">
         <v>5</v>
       </c>
@@ -6567,7 +6574,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="7" t="s">
         <v>5</v>
       </c>
@@ -6584,7 +6591,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="7" t="s">
         <v>5</v>
       </c>
@@ -6601,7 +6608,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="7" t="s">
         <v>5</v>
       </c>
@@ -6618,7 +6625,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" s="7" t="s">
         <v>5</v>
       </c>
@@ -6635,7 +6642,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" s="7" t="s">
         <v>5</v>
       </c>
@@ -6652,7 +6659,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" s="7" t="s">
         <v>5</v>
       </c>
@@ -6669,7 +6676,7 @@
         <v>25200</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" s="7" t="s">
         <v>5</v>
       </c>
@@ -6686,7 +6693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="7" t="s">
         <v>5</v>
       </c>
@@ -6703,7 +6710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" s="11" t="s">
         <v>5</v>
       </c>
@@ -6721,7 +6728,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="11" t="s">
         <v>5</v>
       </c>
@@ -6739,7 +6746,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" s="11" t="s">
         <v>5</v>
       </c>
@@ -6757,7 +6764,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="11" t="s">
         <v>5</v>
       </c>
@@ -6775,7 +6782,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="11" t="s">
         <v>5</v>
       </c>
@@ -6793,7 +6800,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" s="11" t="s">
         <v>5</v>
       </c>
@@ -6811,7 +6818,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" s="11" t="s">
         <v>5</v>
       </c>
@@ -6829,7 +6836,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" s="11" t="s">
         <v>5</v>
       </c>
@@ -6847,7 +6854,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" s="11" t="s">
         <v>5</v>
       </c>
@@ -6865,7 +6872,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" s="11" t="s">
         <v>5</v>
       </c>
@@ -6883,7 +6890,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" s="11" t="s">
         <v>5</v>
       </c>
@@ -6901,7 +6908,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" s="11" t="s">
         <v>5</v>
       </c>
@@ -6919,7 +6926,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" s="11" t="s">
         <v>5</v>
       </c>
@@ -6937,7 +6944,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" s="11" t="s">
         <v>5</v>
       </c>
@@ -6955,7 +6962,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168" s="11" t="s">
         <v>5</v>
       </c>
@@ -6973,7 +6980,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" s="11" t="s">
         <v>5</v>
       </c>
@@ -6991,7 +6998,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" s="11" t="s">
         <v>5</v>
       </c>
@@ -7009,7 +7016,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" s="11" t="s">
         <v>5</v>
       </c>
@@ -7027,7 +7034,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
         <v>5</v>
       </c>
@@ -7045,7 +7052,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" s="11" t="s">
         <v>5</v>
       </c>
@@ -7063,7 +7070,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" s="11" t="s">
         <v>5</v>
       </c>
@@ -7081,7 +7088,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" s="11" t="s">
         <v>5</v>
       </c>
@@ -7099,7 +7106,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" s="11" t="s">
         <v>5</v>
       </c>
@@ -7117,7 +7124,7 @@
         <v>73.710000000000008</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177" s="11" t="s">
         <v>5</v>
       </c>
@@ -7135,7 +7142,7 @@
         <v>73.710000000000008</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A178" s="11" t="s">
         <v>5</v>
       </c>
@@ -7153,7 +7160,7 @@
         <v>6804</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A179" s="11" t="s">
         <v>5</v>
       </c>
@@ -7171,7 +7178,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180" s="11" t="s">
         <v>5</v>
       </c>
@@ -7189,7 +7196,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181" s="7" t="s">
         <v>4</v>
       </c>
@@ -7207,7 +7214,7 @@
         <v>950000</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182" s="7" t="s">
         <v>4</v>
       </c>
@@ -7225,7 +7232,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" s="7" t="s">
         <v>4</v>
       </c>
@@ -7243,7 +7250,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="7" t="s">
         <v>4</v>
       </c>
@@ -7261,7 +7268,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="7" t="s">
         <v>4</v>
       </c>
@@ -7279,7 +7286,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" s="7" t="s">
         <v>4</v>
       </c>
@@ -7297,7 +7304,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A187" s="7" t="s">
         <v>4</v>
       </c>
@@ -7315,7 +7322,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A188" s="7" t="s">
         <v>4</v>
       </c>
@@ -7333,7 +7340,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="7" t="s">
         <v>4</v>
       </c>
@@ -7351,7 +7358,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190" s="7" t="s">
         <v>4</v>
       </c>
@@ -7369,7 +7376,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="7" t="s">
         <v>4</v>
       </c>
@@ -7387,7 +7394,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192" s="7" t="s">
         <v>4</v>
       </c>
@@ -7405,7 +7412,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="7" t="s">
         <v>4</v>
       </c>
@@ -7423,7 +7430,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="7" t="s">
         <v>4</v>
       </c>
@@ -7441,7 +7448,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="7" t="s">
         <v>4</v>
       </c>
@@ -7459,7 +7466,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A196" s="7" t="s">
         <v>4</v>
       </c>
@@ -7477,7 +7484,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="7" t="s">
         <v>4</v>
       </c>
@@ -7495,7 +7502,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" s="7" t="s">
         <v>4</v>
       </c>
@@ -7513,7 +7520,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="7" t="s">
         <v>4</v>
       </c>
@@ -7531,7 +7538,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" s="7" t="s">
         <v>4</v>
       </c>
@@ -7549,7 +7556,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="7" t="s">
         <v>4</v>
       </c>
@@ -7567,7 +7574,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A202" s="7" t="s">
         <v>4</v>
       </c>
@@ -7585,7 +7592,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="7" t="s">
         <v>4</v>
       </c>
@@ -7603,7 +7610,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204" s="7" t="s">
         <v>4</v>
       </c>
@@ -7621,7 +7628,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="7" t="s">
         <v>4</v>
       </c>
@@ -7639,7 +7646,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A206" s="7" t="s">
         <v>4</v>
       </c>
@@ -7657,7 +7664,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="11" t="s">
         <v>6</v>
       </c>
@@ -7684,16 +7691,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F92"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.69140625" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="17" style="10" customWidth="1"/>
-    <col min="3" max="3" width="47.84375" customWidth="1"/>
+    <col min="3" max="3" width="47.86328125" customWidth="1"/>
     <col min="4" max="4" width="9" style="10" customWidth="1"/>
-    <col min="5" max="5" width="13.23046875" customWidth="1"/>
+    <col min="5" max="5" width="13.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="38" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -7710,7 +7717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="14.85" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
@@ -7727,7 +7734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -7744,7 +7751,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -7761,7 +7768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
         <v>2</v>
       </c>
@@ -7778,7 +7785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
         <v>2</v>
       </c>
@@ -7795,7 +7802,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -7812,7 +7819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
         <v>3</v>
       </c>
@@ -7829,7 +7836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
         <v>3</v>
       </c>
@@ -7846,7 +7853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -7863,7 +7870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="s">
         <v>3</v>
       </c>
@@ -7880,7 +7887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
         <v>4</v>
       </c>
@@ -7897,7 +7904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="s">
         <v>4</v>
       </c>
@@ -7914,7 +7921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="s">
         <v>4</v>
       </c>
@@ -7931,7 +7938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
         <v>4</v>
       </c>
@@ -7948,7 +7955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
         <v>4</v>
       </c>
@@ -7965,7 +7972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="s">
         <v>4</v>
       </c>
@@ -7982,7 +7989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
         <v>4</v>
       </c>
@@ -7999,7 +8006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="s">
         <v>4</v>
       </c>
@@ -8016,7 +8023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="s">
         <v>4</v>
       </c>
@@ -8033,7 +8040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="s">
         <v>4</v>
       </c>
@@ -8050,7 +8057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="s">
         <v>4</v>
       </c>
@@ -8067,7 +8074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
         <v>4</v>
       </c>
@@ -8084,7 +8091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="s">
         <v>4</v>
       </c>
@@ -8101,7 +8108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
         <v>4</v>
       </c>
@@ -8118,7 +8125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
         <v>5</v>
       </c>
@@ -8135,7 +8142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="s">
         <v>5</v>
       </c>
@@ -8152,7 +8159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="s">
         <v>5</v>
       </c>
@@ -8169,7 +8176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
@@ -8186,7 +8193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="s">
         <v>5</v>
       </c>
@@ -8203,7 +8210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="7" t="s">
         <v>5</v>
       </c>
@@ -8220,7 +8227,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
         <v>5</v>
       </c>
@@ -8237,7 +8244,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="s">
         <v>5</v>
       </c>
@@ -8254,7 +8261,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
         <v>5</v>
       </c>
@@ -8271,7 +8278,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
         <v>5</v>
       </c>
@@ -8288,7 +8295,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="7" t="s">
         <v>5</v>
       </c>
@@ -8305,7 +8312,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="7" t="s">
         <v>5</v>
       </c>
@@ -8322,7 +8329,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
         <v>5</v>
       </c>
@@ -8339,7 +8346,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
         <v>5</v>
       </c>
@@ -8356,7 +8363,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="s">
         <v>5</v>
       </c>
@@ -8373,7 +8380,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="7" t="s">
         <v>5</v>
       </c>
@@ -8390,7 +8397,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="7" t="s">
         <v>5</v>
       </c>
@@ -8407,7 +8414,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="7" t="s">
         <v>5</v>
       </c>
@@ -8424,7 +8431,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="7" t="s">
         <v>5</v>
       </c>
@@ -8441,7 +8448,7 @@
         <v>25200</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
         <v>5</v>
       </c>
@@ -8458,7 +8465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
         <v>5</v>
       </c>
@@ -8475,7 +8482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="11" t="s">
         <v>5</v>
       </c>
@@ -8493,7 +8500,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="11" t="s">
         <v>5</v>
       </c>
@@ -8511,7 +8518,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="11" t="s">
         <v>5</v>
       </c>
@@ -8529,7 +8536,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="11" t="s">
         <v>5</v>
       </c>
@@ -8547,7 +8554,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="11" t="s">
         <v>5</v>
       </c>
@@ -8565,7 +8572,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="11" t="s">
         <v>5</v>
       </c>
@@ -8583,7 +8590,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="11" t="s">
         <v>5</v>
       </c>
@@ -8601,7 +8608,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="11" t="s">
         <v>5</v>
       </c>
@@ -8619,7 +8626,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="11" t="s">
         <v>5</v>
       </c>
@@ -8637,7 +8644,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="11" t="s">
         <v>5</v>
       </c>
@@ -8655,7 +8662,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="11" t="s">
         <v>5</v>
       </c>
@@ -8673,7 +8680,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="11" t="s">
         <v>5</v>
       </c>
@@ -8691,7 +8698,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" s="11" t="s">
         <v>5</v>
       </c>
@@ -8709,7 +8716,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="11" t="s">
         <v>5</v>
       </c>
@@ -8727,7 +8734,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="11" t="s">
         <v>5</v>
       </c>
@@ -8745,7 +8752,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="11" t="s">
         <v>5</v>
       </c>
@@ -8763,7 +8770,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="11" t="s">
         <v>5</v>
       </c>
@@ -8781,7 +8788,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="11" t="s">
         <v>5</v>
       </c>
@@ -8799,7 +8806,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="11" t="s">
         <v>5</v>
       </c>
@@ -8817,7 +8824,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" s="11" t="s">
         <v>5</v>
       </c>
@@ -8835,7 +8842,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" s="11" t="s">
         <v>5</v>
       </c>
@@ -8853,7 +8860,7 @@
         <v>8.0460000000000012</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" s="11" t="s">
         <v>5</v>
       </c>
@@ -8871,7 +8878,7 @@
         <v>73.710000000000008</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" s="11" t="s">
         <v>5</v>
       </c>
@@ -8889,7 +8896,7 @@
         <v>73.710000000000008</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="11" t="s">
         <v>5</v>
       </c>
@@ -8907,7 +8914,7 @@
         <v>6804</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" s="11" t="s">
         <v>5</v>
       </c>
@@ -8925,7 +8932,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="11" t="s">
         <v>5</v>
       </c>
@@ -8943,7 +8950,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" s="7" t="s">
         <v>4</v>
       </c>
@@ -8962,7 +8969,7 @@
       </c>
       <c r="F73" s="14"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" s="7" t="s">
         <v>4</v>
       </c>
@@ -8980,7 +8987,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" s="7" t="s">
         <v>4</v>
       </c>
@@ -8998,7 +9005,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" s="7" t="s">
         <v>4</v>
       </c>
@@ -9016,7 +9023,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" s="7" t="s">
         <v>4</v>
       </c>
@@ -9034,7 +9041,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" s="7" t="s">
         <v>4</v>
       </c>
@@ -9052,7 +9059,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="7" t="s">
         <v>4</v>
       </c>
@@ -9070,7 +9077,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="7" t="s">
         <v>4</v>
       </c>
@@ -9088,7 +9095,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="7" t="s">
         <v>4</v>
       </c>
@@ -9106,7 +9113,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="7" t="s">
         <v>4</v>
       </c>
@@ -9124,7 +9131,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="7" t="s">
         <v>4</v>
       </c>
@@ -9142,7 +9149,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="7" t="s">
         <v>4</v>
       </c>
@@ -9160,7 +9167,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="7" t="s">
         <v>4</v>
       </c>
@@ -9178,7 +9185,7 @@
         <v>880000</v>
       </c>
     </row>
-    <row r="86" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A86" s="7" t="s">
         <v>4</v>
       </c>
@@ -9196,7 +9203,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="87" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A87" s="7" t="s">
         <v>4</v>
       </c>
@@ -9214,7 +9221,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="7" t="s">
         <v>4</v>
       </c>
@@ -9232,7 +9239,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="7" t="s">
         <v>4</v>
       </c>
@@ -9250,7 +9257,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="7" t="s">
         <v>4</v>
       </c>
@@ -9268,7 +9275,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="7" t="s">
         <v>4</v>
       </c>
@@ -9286,7 +9293,7 @@
         <v>950000</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="11" t="s">
         <v>6</v>
       </c>
@@ -9313,9 +9320,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF990EF-DE90-47BF-B8CD-C4AE8A165117}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
@@ -9332,7 +9339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
@@ -9349,7 +9356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
@@ -9366,7 +9373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
@@ -9383,7 +9390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
@@ -9408,7 +9415,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C5D093-8CF0-451E-9E06-02EB1F70D6E7}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
